--- a/data/trans_camb/P1421-Clase-trans_camb.xlsx
+++ b/data/trans_camb/P1421-Clase-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>2,87</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,71</t>
+          <t>2,58</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,7; -0,88</t>
+          <t>-4,48; -0,73</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 2,14</t>
+          <t>-2,44; 2,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,5</t>
+          <t>-0,76; 4,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,89; 4,67</t>
+          <t>-3,32; 4,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,07; 0,41</t>
+          <t>-6,65; 0,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 6,67</t>
+          <t>-1,19; 6,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,93</t>
+          <t>-3,13; 0,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 0,75</t>
+          <t>-3,09; 0,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,57; 4,76</t>
+          <t>0,59; 4,64</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,62%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>56,99%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 6,58</t>
+          <t>-100,0; 9,29</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-59,04; 98,43</t>
+          <t>-56,72; 105,45</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-13,48; 223,95</t>
+          <t>-20,7; 189,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,28; 107,16</t>
+          <t>-39,92; 101,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,15; 19,73</t>
+          <t>-74,39; 12,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 160,02</t>
+          <t>-13,35; 140,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-56,16; 28,71</t>
+          <t>-55,89; 28,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,13; 23,23</t>
+          <t>-55,85; 31,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 139,21</t>
+          <t>8,83; 132,06</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,04</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,55</t>
+          <t>1,56</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,14</t>
+          <t>-3,24; 0,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 0,01</t>
+          <t>-3,62; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 3,33</t>
+          <t>-1,35; 3,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 0,56</t>
+          <t>-6,89; 0,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,52; 0,82</t>
+          <t>-6,33; 0,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 6,57</t>
+          <t>-1,22; 6,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; -0,64</t>
+          <t>-4,62; -0,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; -0,17</t>
+          <t>-4,59; -0,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,67</t>
+          <t>-0,76; 3,81</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-89,21; 54,79</t>
+          <t>-90,95; 39,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 57,29</t>
+          <t>-100,0; 32,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,4; 230,43</t>
+          <t>-41,11; 253,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-69,56; 9,96</t>
+          <t>-70,46; 8,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 15,86</t>
+          <t>-64,5; 17,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 108,35</t>
+          <t>-13,36; 103,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,38; -12,34</t>
+          <t>-73,37; -11,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,41; -2,47</t>
+          <t>-70,38; -4,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-14,94; 87,3</t>
+          <t>-13,38; 98,32</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,34</t>
+          <t>1,98</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,61</t>
+          <t>6,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,42</t>
+          <t>3,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 0,18</t>
+          <t>-3,26; 0,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,51; -0,35</t>
+          <t>-3,82; -0,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 3,29</t>
+          <t>-0,25; 5,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 2,99</t>
+          <t>-7,53; 2,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,63; 5,55</t>
+          <t>-5,88; 6,23</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 12,18</t>
+          <t>0,96; 12,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 0,59</t>
+          <t>-2,77; 0,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 0,41</t>
+          <t>-3,08; 0,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 4,35</t>
+          <t>1,11; 6,19</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>72,8%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>94,68%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-79,02; 18,65</t>
+          <t>-80,46; 19,6</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-91,46; 3,56</t>
+          <t>-92,87; -2,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,12; 151,88</t>
+          <t>-11,83; 265,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 76,54</t>
+          <t>-65,9; 70,85</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,38; 124,52</t>
+          <t>-60,45; 142,49</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,25; 300,01</t>
+          <t>4,49; 272,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-59,66; 25,51</t>
+          <t>-59,18; 27,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,22; 18,69</t>
+          <t>-65,76; 25,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 130,82</t>
+          <t>18,4; 211,91</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,45</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,19</t>
+          <t>5,84</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3,28</t>
+          <t>4,06</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,15</t>
+          <t>-2,08; 0,11</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,5; -0,42</t>
+          <t>-2,42; -0,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,24</t>
+          <t>0,68; 3,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 1,08</t>
+          <t>-3,66; 1,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 1,28</t>
+          <t>-3,68; 1,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 6,87</t>
+          <t>3,12; 8,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 0,23</t>
+          <t>-2,03; 0,27</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,28; -0,04</t>
+          <t>-2,24; -0,03</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,83</t>
+          <t>2,59; 5,55</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>107,1%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>108,83%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-68,8; 9,6</t>
+          <t>-67,87; 9,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-85,02; -18,29</t>
+          <t>-82,72; -17,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27,69; 249,81</t>
+          <t>17,89; 216,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-48,86; 23,03</t>
+          <t>-47,92; 23,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-45,93; 27,8</t>
+          <t>-49,11; 28,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-23,44; 128,24</t>
+          <t>40,25; 172,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-47,6; 9,14</t>
+          <t>-45,86; 9,55</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-51,87; 0,58</t>
+          <t>-50,55; -0,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,71; 148,39</t>
+          <t>58,73; 176,16</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,75</t>
+          <t>7,8</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5,41</t>
+          <t>5,52</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 0,25</t>
+          <t>-3,92; 0,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 1,87</t>
+          <t>-2,66; 1,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,69</t>
+          <t>-0,29; 5,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 3,68</t>
+          <t>-1,73; 3,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,63</t>
+          <t>-1,03; 4,81</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 10,13</t>
+          <t>5,0; 10,32</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,64</t>
+          <t>-1,71; 1,85</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 2,45</t>
+          <t>-1,11; 2,67</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 7,76</t>
+          <t>3,58; 7,48</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>113,12%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>122,71%</t>
+          <t>141,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>123,69%</t>
+          <t>126,1%</t>
         </is>
       </c>
     </row>
@@ -1647,54 +1647,54 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-88,3; 41,42</t>
+          <t>-87,4; 57,94</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-62,36; 162,46</t>
+          <t>-60,56; 154,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 478,79</t>
+          <t>-13,3; 375,49</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,94; 93,8</t>
+          <t>-25,33; 88,05</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 115,98</t>
+          <t>-15,64; 114,04</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,7; 249,22</t>
+          <t>63,26; 254,14</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-37,53; 47,89</t>
+          <t>-32,85; 57,97</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-24,55; 70,45</t>
+          <t>-21,71; 81,61</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>57,09; 239,79</t>
+          <t>60,49; 223,59</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,52</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,74</t>
+          <t>3,63</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,28</t>
+          <t>-1,19; 2,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 1,17</t>
+          <t>-1,52; 1,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 6,21</t>
+          <t>-0,16; 6,41</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,44</t>
+          <t>-1,91; 1,51</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 2,21</t>
+          <t>-1,4; 2,2</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,84</t>
+          <t>1,97; 6,44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,33</t>
+          <t>-1,52; 1,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,66</t>
+          <t>-1,25; 1,68</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,59</t>
+          <t>1,86; 5,48</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>220,64%</t>
+          <t>232,42%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>94,8%</t>
         </is>
       </c>
     </row>
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-48,63; —</t>
+          <t>-64,95; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-36,26; 39,44</t>
+          <t>-37,21; 39,1</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-25,72; 60,61</t>
+          <t>-27,52; 57,48</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>43,54; 178,71</t>
+          <t>36,98; 169,66</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-35,52; 40,38</t>
+          <t>-34,82; 40,62</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-27,27; 52,74</t>
+          <t>-28,7; 51,46</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>39,4; 168,36</t>
+          <t>37,67; 165,16</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,87</t>
+          <t>2,02</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,61</t>
+          <t>5,41</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3,3</t>
+          <t>3,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,82; -0,55</t>
+          <t>-1,86; -0,56</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,68; -0,37</t>
+          <t>-1,69; -0,36</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,78</t>
+          <t>1,13; 2,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,61</t>
+          <t>-1,49; 0,72</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,82</t>
+          <t>-1,36; 0,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,45; 5,98</t>
+          <t>4,15; 6,65</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,4; -0,13</t>
+          <t>-1,5; -0,16</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,11</t>
+          <t>-1,24; 0,08</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,25</t>
+          <t>2,94; 4,5</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>84,12%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-65,04; -25,47</t>
+          <t>-66,13; -24,95</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-60,14; -16,42</t>
+          <t>-59,11; -15,04</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>30,13; 136,72</t>
+          <t>39,12; 149,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 11,5</t>
+          <t>-23,49; 14,1</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 15,93</t>
+          <t>-21,74; 17,7</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>43,65; 115,57</t>
+          <t>65,94; 129,01</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-31,71; -3,28</t>
+          <t>-32,74; -4,17</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-28,25; 2,88</t>
+          <t>-27,92; 2,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>52,42; 112,25</t>
+          <t>66,08; 120,2</t>
         </is>
       </c>
     </row>
